--- a/assets/constructions/examples/ctd_mr2.xlsx
+++ b/assets/constructions/examples/ctd_mr2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,46 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>fhamin</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>fhamax</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SGED290150108</t>
+          <t>SEME6112015</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -638,46 +673,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SGED29</t>
+          <t>SEME61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
       <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>18</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>2.3</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -698,33 +737,29 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0/-0,012</t>
+          <t>0/-0,015</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NGHM</t>
+          <t>Micro Grain Carbide</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DLC</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>YG STD</t>
-        </is>
-      </c>
+          <t>Y-Coating</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="n">
         <v>30</v>
@@ -739,7 +774,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2017 - YG1 - General catalogue</t>
+          <t>2017 - YG1 - YE-4G13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -752,65 +787,78 @@
       </c>
       <c r="AM2" t="b">
         <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PKH</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEME620040050203</t>
+          <t>57NE16026W WS15PE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEME6</t>
+          <t>57NE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>PMSH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>K</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6</v>
+        <v>32</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>32</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>15.04</v>
+      </c>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -820,7 +868,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -831,18 +879,18 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0/-0,012</t>
+          <t>e8</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Micro Grain Carbide</t>
+          <t>WS15PE</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Y-Coating</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -850,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AB3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AC3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -868,7 +916,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2020: www.yg1.co.kr/toolselection/main/</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -880,66 +928,75 @@
         <v>0</v>
       </c>
       <c r="AM3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3562 8.015</t>
+          <t>51N306002.. UNCOATED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GUHRING</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>51N3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SH</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>5.4</v>
+      </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -953,39 +1010,39 @@
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>h10</t>
+          <t>e8</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>UNCOATED</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>FIRE</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>DIN 6527 L</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
         <v>63</v>
       </c>
       <c r="AC4" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -997,7 +1054,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2020 www.guhring.com</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1009,13 +1066,26 @@
         <v>0</v>
       </c>
       <c r="AM4" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEME6101200508</t>
+          <t>SEME640250210E</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1025,7 +1095,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEME6</t>
+          <t>SEME64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1039,32 +1109,32 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1089,7 +1159,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0/-0,012</t>
+          <t>0/-0,03</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1140,64 +1210,87 @@
       <c r="AM5" t="b">
         <v>0</v>
       </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4457.87</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PKH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MPXLRBD0120R020N100</t>
+          <t>G8A36905</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MITSUBISHI</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MPXLRB</t>
+          <t>G8A36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MNS</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.8</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.16</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1211,17 +1304,25 @@
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0/-0,01</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>0/-0,015</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Nano Grain Carbide</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Blue-Coating</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1229,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AC6" t="n">
         <v>30</v>
@@ -1247,7 +1348,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2020 / Mitsubishi Website</t>
+          <t>2017 - YG1 - General catalogue</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1256,10 +1357,31 @@
         </is>
       </c>
       <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
         <v>1</v>
       </c>
-      <c r="AM6" t="b">
-        <v>0</v>
+      <c r="AO6" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4671.15</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
       </c>
     </row>
   </sheetData>
